--- a/job-filters.xlsx
+++ b/job-filters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Shubham\fiverr\raikaphotograph\task-schedular\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1579B3-00CA-4EED-A5A8-A782D59BE46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC15EBB1-5B75-4B17-B91A-3A466E8CD984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -288,7 +288,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -650,7 +650,7 @@
         <v>26</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>17</v>

--- a/job-filters.xlsx
+++ b/job-filters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Shubham\fiverr\raikaphotograph\task-schedular\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC15EBB1-5B75-4B17-B91A-3A466E8CD984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F3C3DEF-5351-4C46-9DFB-D98DB787BA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="42">
   <si>
     <t>Job Name</t>
   </si>
@@ -225,6 +225,54 @@
   <si>
     <t>Male
 Female</t>
+  </si>
+  <si>
+    <t>Business Development Associate
+Senior Sales Associate 
+Business Development Manager
+Business Development Executive
+Business Development Specialist 
+BDE
+Sales Executive
+Sales Officer
+Credit Card Sales Associate 
+Associate / Consultant 
+Insurance Associate
+Team Leader 
+Insurance Agent 
+Insurance Advisor 
+Sales Executive 
+Senior Tele Sales Executive 
+Telecalling Executive
+BPO Tele calling
+BPO Telecalling
+Telecalling 
+Insurance Sales
+Telesales 
+Customer Sales Executive 
+Presale
+Tele Marketing Executive 
+Tele Caller 
+Tele Sales Executive
+Telecaller
+Sales &amp; Marketing Executive
+Senior Tele Caller 
+Telemarketing Executive 
+Call Center Executive 
+Tele Sales Executive
+Credit Card Sales Executive 
+Marketing Executive
+Sales Coordinator 
+Insurance Sales
+Outbound Sales Executive 
+Sales Officer
+Telecalling Executive 
+Insurance
+Call Center Agent 
+Tele Caller
+Inside Sales Executive
+Sales Manager
+BPO Executive</t>
   </si>
 </sst>
 </file>
@@ -582,7 +630,7 @@
     <col min="6" max="6" width="13.44140625" customWidth="1"/>
     <col min="7" max="7" width="13.77734375" customWidth="1"/>
     <col min="10" max="10" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.44140625" customWidth="1"/>
+    <col min="11" max="11" width="37.44140625" customWidth="1"/>
     <col min="12" max="12" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -656,7 +704,7 @@
         <v>17</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>20</v>

--- a/job-filters.xlsx
+++ b/job-filters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Shubham\fiverr\raikaphotograph\task-schedular\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80AD671-5530-4DB7-80CF-991463D768BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B65353E-7AC8-46CB-8B49-CF7ECC105664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="46">
   <si>
     <t>Job Name</t>
   </si>
@@ -276,6 +276,15 @@
   </si>
   <si>
     <t>photographer assistant</t>
+  </si>
+  <si>
+    <t>photography assistant</t>
+  </si>
+  <si>
+    <t>fill:25</t>
+  </si>
+  <si>
+    <t>all</t>
   </si>
 </sst>
 </file>
@@ -741,10 +750,25 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="K4" s="3"/>
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/job-filters.xlsx
+++ b/job-filters.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="49">
   <si>
     <t>Job Name</t>
   </si>
@@ -167,6 +167,10 @@
   </si>
   <si>
     <t>Photographer &amp; Videographer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">radio:Anywhere in the city
+</t>
   </si>
   <si>
     <t>photography assistant</t>
@@ -707,8 +711,8 @@
       <c r="A4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>24</v>
+      <c r="B4" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>14</v>
@@ -730,7 +734,7 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>24</v>
@@ -742,11 +746,11 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="I5" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -1818,34 +1822,34 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
@@ -1873,16 +1877,16 @@
         <v>18</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>20</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>22</v>
@@ -1890,26 +1894,26 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>26</v>

--- a/job-filters.xlsx
+++ b/job-filters.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="49">
   <si>
     <t>Job Name</t>
   </si>
@@ -68,9 +68,6 @@
   </si>
   <si>
     <t>checkbox:English,Kannada</t>
-  </si>
-  <si>
-    <t>dropdown:1 Year</t>
   </si>
   <si>
     <t>checkbox:Twelfth,Graduate</t>
@@ -140,6 +137,9 @@
   </si>
   <si>
     <t>radio:5 KM</t>
+  </si>
+  <si>
+    <t>dropdown:1 Year</t>
   </si>
   <si>
     <t>Professional Photographer 
@@ -660,34 +660,32 @@
       <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>14</v>
@@ -695,10 +693,10 @@
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -720,10 +718,10 @@
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>25</v>
@@ -737,7 +735,7 @@
         <v>29</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>14</v>
@@ -1871,10 +1869,10 @@
         <v>16</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>41</v>
@@ -1883,13 +1881,13 @@
         <v>42</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>43</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -1897,7 +1895,7 @@
         <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>45</v>
@@ -1910,7 +1908,7 @@
         <v>47</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>48</v>
